--- a/implementation_evaluation_forms/001_project_execution_readiness_survey--implementation_evaluation_forms.xlsx
+++ b/implementation_evaluation_forms/001_project_execution_readiness_survey--implementation_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey</t>
+          <t>Project Description</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,20 +548,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>project_execution_readiness</t>
+          <t>Team Lead's Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,20 +571,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>project_execution_readiness</t>
+          <t>Project Start Date</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +594,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>project_execution_readiness</t>
+          <t>Number of Projects Executed</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>project_execution_readiness</t>
+          <t>Project Type</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>project_execution_readiness</t>
+          <t>Project Duration</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,20 +663,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>project_execution_readiness</t>
+          <t>Project Status</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,13 +686,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>project_execution_readiness</t>
+          <t>Team Size</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,20 +709,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>project_execution</t>
+          <t>Project Lead's Email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey</t>
+          <t>Project Lead's Phone Number</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>project_execution_readiness</t>
+          <t>Project Lead's Availability</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,13 +778,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey</t>
+          <t>Project Execution Date</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -801,11 +801,126 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>project_execution</t>
+          <t>Project Budget</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>project_execution_readiness_survey_14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Project Timeline</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>project_execution_readiness_survey_15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Project Goals</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>project_execution_readiness_survey_16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Project Risks</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>project_execution_readiness_survey_17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Project Challenges</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>project_execution_readiness_survey_18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -822,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,68 +965,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_4_choices</t>
+          <t>project_execution_readiness_survey_5_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>waterfall</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Waterfall</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_4_choices</t>
+          <t>project_execution_readiness_survey_5_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>agile</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Agile</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_10_choices</t>
+          <t>project_execution_readiness_survey_5_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_10_choices</t>
+          <t>project_execution_readiness_survey_7_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>In Progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>project_execution_readiness_survey_7_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>on_track</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>project_execution_readiness_survey_7_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>delayed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Delayed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>project_execution_readiness_survey_7_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
     </row>
